--- a/evaluations/test_reports/throughput/Increasing_Clients/direct_client/workload.xlsx
+++ b/evaluations/test_reports/throughput/Increasing_Clients/direct_client/workload.xlsx
@@ -453,7 +453,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>4.789193471272786</v>
+        <v>12.01070900316592</v>
       </c>
     </row>
     <row r="3">
@@ -461,10 +461,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>1.5</v>
+        <v>40.5</v>
       </c>
       <c r="C3" t="n">
-        <v>29.60677941640218</v>
+        <v>11.87533514771766</v>
       </c>
     </row>
     <row r="4">
@@ -472,10 +472,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>1.875</v>
+        <v>92.66666649999999</v>
       </c>
       <c r="C4" t="n">
-        <v>154.000072819846</v>
+        <v>14.61277136574161</v>
       </c>
     </row>
     <row r="5">
@@ -483,10 +483,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>108.2</v>
       </c>
       <c r="C5" t="n">
-        <v>434.7224090343867</v>
+        <v>16.72173833197969</v>
       </c>
     </row>
     <row r="6">
@@ -494,10 +494,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>2.3</v>
+        <v>119.095238</v>
       </c>
       <c r="C6" t="n">
-        <v>400.9523562022618</v>
+        <v>18.73920741612027</v>
       </c>
     </row>
     <row r="7">
@@ -505,10 +505,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>1.6</v>
+        <v>126.5</v>
       </c>
       <c r="C7" t="n">
-        <v>390.4873831518765</v>
+        <v>20.6384538511354</v>
       </c>
     </row>
     <row r="8">
@@ -516,10 +516,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.8</v>
+        <v>132.05</v>
       </c>
       <c r="C8" t="n">
-        <v>380.3646723429362</v>
+        <v>22.20677701457868</v>
       </c>
     </row>
     <row r="9">
@@ -527,10 +527,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3333333333333333</v>
+        <v>144.9</v>
       </c>
       <c r="C9" t="n">
-        <v>521.8050257772462</v>
+        <v>23.82508986389175</v>
       </c>
     </row>
     <row r="10">
@@ -538,10 +538,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2</v>
+        <v>149.75</v>
       </c>
       <c r="C10" t="n">
-        <v>953.917956352234</v>
+        <v>25.54351759967402</v>
       </c>
     </row>
     <row r="11">
@@ -549,10 +549,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.4</v>
+        <v>151.75</v>
       </c>
       <c r="C11" t="n">
-        <v>1102.544079131858</v>
+        <v>27.15257557032881</v>
       </c>
     </row>
     <row r="12">
@@ -560,10 +560,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>153.1</v>
       </c>
       <c r="C12" t="n">
-        <v>1548.422447470731</v>
+        <v>28.72662565393433</v>
       </c>
     </row>
     <row r="13">
@@ -571,10 +571,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.35</v>
+        <v>156.85</v>
       </c>
       <c r="C13" t="n">
-        <v>2626.200621456497</v>
+        <v>30.05264077676924</v>
       </c>
     </row>
     <row r="14">
@@ -582,10 +582,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>1.7</v>
+        <v>154.65</v>
       </c>
       <c r="C14" t="n">
-        <v>2767.863361062132</v>
+        <v>31.39837493895655</v>
       </c>
     </row>
     <row r="15">
@@ -593,10 +593,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>1.6</v>
+        <v>158.8</v>
       </c>
       <c r="C15" t="n">
-        <v>2812.703151551504</v>
+        <v>32.73452982420105</v>
       </c>
     </row>
     <row r="16">
@@ -604,10 +604,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>1.625</v>
+        <v>158.8</v>
       </c>
       <c r="C16" t="n">
-        <v>2829.002107448756</v>
+        <v>34.13196836467949</v>
       </c>
     </row>
     <row r="17">
@@ -615,10 +615,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.8</v>
+        <v>158.3</v>
       </c>
       <c r="C17" t="n">
-        <v>3211.620213328928</v>
+        <v>35.46344146394857</v>
       </c>
     </row>
     <row r="18">
@@ -626,10 +626,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.6</v>
+        <v>163.2</v>
       </c>
       <c r="C18" t="n">
-        <v>3492.014030930857</v>
+        <v>36.92018610475154</v>
       </c>
     </row>
     <row r="19">
@@ -637,10 +637,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6</v>
+        <v>162.75</v>
       </c>
       <c r="C19" t="n">
-        <v>3653.926564587487</v>
+        <v>38.56694099424988</v>
       </c>
     </row>
     <row r="20">
@@ -648,10 +648,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.4</v>
+        <v>162.3</v>
       </c>
       <c r="C20" t="n">
-        <v>3860.909532862893</v>
+        <v>40.1901316731897</v>
       </c>
     </row>
     <row r="21">
@@ -659,10 +659,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.3</v>
+        <v>161.8</v>
       </c>
       <c r="C21" t="n">
-        <v>4091.970383326213</v>
+        <v>41.34920553262405</v>
       </c>
     </row>
     <row r="22">
@@ -670,10 +670,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.3</v>
+        <v>161.6</v>
       </c>
       <c r="C22" t="n">
-        <v>4015.767505024419</v>
+        <v>42.71296559173661</v>
       </c>
     </row>
     <row r="23">
@@ -681,10 +681,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.475</v>
+        <v>155.6</v>
       </c>
       <c r="C23" t="n">
-        <v>4613.721923067978</v>
+        <v>44.49287993238005</v>
       </c>
     </row>
     <row r="24">
@@ -692,10 +692,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.5333333333333333</v>
+        <v>148.8</v>
       </c>
       <c r="C24" t="n">
-        <v>4558.6346229305</v>
+        <v>46.05293714464196</v>
       </c>
     </row>
     <row r="25">
@@ -703,10 +703,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.8</v>
+        <v>148.75</v>
       </c>
       <c r="C25" t="n">
-        <v>4654.28687561126</v>
+        <v>47.63418443514729</v>
       </c>
     </row>
     <row r="26">
@@ -714,10 +714,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.6999999999999998</v>
+        <v>149.4</v>
       </c>
       <c r="C26" t="n">
-        <v>4548.597249873849</v>
+        <v>49.36139085708533</v>
       </c>
     </row>
     <row r="27">
@@ -725,10 +725,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.6</v>
+        <v>150.25</v>
       </c>
       <c r="C27" t="n">
-        <v>4590.198699029427</v>
+        <v>51.31041957283077</v>
       </c>
     </row>
     <row r="28">
@@ -736,10 +736,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.3</v>
+        <v>152.1</v>
       </c>
       <c r="C28" t="n">
-        <v>4715.003046496161</v>
+        <v>53.25312440497296</v>
       </c>
     </row>
     <row r="29">
@@ -747,10 +747,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.25</v>
+        <v>151.7</v>
       </c>
       <c r="C29" t="n">
-        <v>4732.815192784636</v>
+        <v>54.8456177802857</v>
       </c>
     </row>
     <row r="30">
@@ -758,10 +758,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.1</v>
+        <v>153.3</v>
       </c>
       <c r="C30" t="n">
-        <v>5352.698741670265</v>
+        <v>56.33622612894324</v>
       </c>
     </row>
     <row r="31">
@@ -769,10 +769,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.5</v>
+        <v>154.4</v>
       </c>
       <c r="C31" t="n">
-        <v>5646.062366587705</v>
+        <v>57.95256104545906</v>
       </c>
     </row>
     <row r="32">
@@ -780,10 +780,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>0.6</v>
+        <v>155.6</v>
       </c>
       <c r="C32" t="n">
-        <v>5885.494088133176</v>
+        <v>59.42384868618576</v>
       </c>
     </row>
     <row r="33">
@@ -791,10 +791,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>0.75</v>
+        <v>156.8</v>
       </c>
       <c r="C33" t="n">
-        <v>6500.109788086308</v>
+        <v>61.26073181331297</v>
       </c>
     </row>
     <row r="34">
@@ -802,10 +802,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>1.633333333333334</v>
+        <v>155.3</v>
       </c>
       <c r="C34" t="n">
-        <v>6429.973723769228</v>
+        <v>62.50846659295949</v>
       </c>
     </row>
     <row r="35">
@@ -813,10 +813,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>2.166666666666667</v>
+        <v>155.75</v>
       </c>
       <c r="C35" t="n">
-        <v>6668.168307612716</v>
+        <v>63.78913650142358</v>
       </c>
     </row>
     <row r="36">
@@ -824,10 +824,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>2.2</v>
+        <v>152.7</v>
       </c>
       <c r="C36" t="n">
-        <v>6634.180061278804</v>
+        <v>65.38276730929172</v>
       </c>
     </row>
     <row r="37">
@@ -835,10 +835,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>1.275</v>
+        <v>155.15</v>
       </c>
       <c r="C37" t="n">
-        <v>6838.900594520652</v>
+        <v>66.82697145513252</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>0.7666666666666666</v>
+        <v>156.65</v>
       </c>
       <c r="C38" t="n">
-        <v>7319.337431224078</v>
+        <v>68.30473542759933</v>
       </c>
     </row>
     <row r="39">
@@ -857,10 +857,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>0.6</v>
+        <v>166</v>
       </c>
       <c r="C39" t="n">
-        <v>7463.593998493618</v>
+        <v>69.84308143548532</v>
       </c>
     </row>
     <row r="40">
@@ -868,10 +868,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>0.5</v>
+        <v>168.8</v>
       </c>
       <c r="C40" t="n">
-        <v>7993.504442951896</v>
+        <v>71.49345250622754</v>
       </c>
     </row>
     <row r="41">
@@ -879,10 +879,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>0.525</v>
+        <v>168.9</v>
       </c>
       <c r="C41" t="n">
-        <v>8589.99135786031</v>
+        <v>73.45166931455455</v>
       </c>
     </row>
     <row r="42">
@@ -890,10 +890,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>0.575</v>
+        <v>163.55</v>
       </c>
       <c r="C42" t="n">
-        <v>8654.784026189105</v>
+        <v>75.09818688890581</v>
       </c>
     </row>
     <row r="43">
@@ -901,10 +901,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>0.75</v>
+        <v>158.85</v>
       </c>
       <c r="C43" t="n">
-        <v>9091.900681567564</v>
+        <v>76.55912431633732</v>
       </c>
     </row>
     <row r="44">
@@ -912,10 +912,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>0.8</v>
+        <v>156.6</v>
       </c>
       <c r="C44" t="n">
-        <v>9610.765450190323</v>
+        <v>78.22065708485994</v>
       </c>
     </row>
     <row r="45">
@@ -923,10 +923,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>0.9</v>
+        <v>153.2</v>
       </c>
       <c r="C45" t="n">
-        <v>9646.504229347178</v>
+        <v>79.52171336283774</v>
       </c>
     </row>
     <row r="46">
@@ -934,10 +934,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>0.7666666666666666</v>
+        <v>154.8</v>
       </c>
       <c r="C46" t="n">
-        <v>9599.317961062732</v>
+        <v>80.85887439098403</v>
       </c>
     </row>
     <row r="47">
@@ -945,10 +945,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>1.05</v>
+        <v>156.9</v>
       </c>
       <c r="C47" t="n">
-        <v>9964.849321161633</v>
+        <v>82.58332795317526</v>
       </c>
     </row>
     <row r="48">
@@ -956,10 +956,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>1.1</v>
+        <v>157.95</v>
       </c>
       <c r="C48" t="n">
-        <v>9905.589792626037</v>
+        <v>84.64316081377657</v>
       </c>
     </row>
     <row r="49">
@@ -967,10 +967,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>1.25</v>
+        <v>153.1</v>
       </c>
       <c r="C49" t="n">
-        <v>9816.762221629851</v>
+        <v>86.54850204143037</v>
       </c>
     </row>
     <row r="50">
@@ -978,10 +978,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>150.55</v>
       </c>
       <c r="C50" t="n">
-        <v>9672.836219065288</v>
+        <v>88.51620362650134</v>
       </c>
     </row>
     <row r="51">
@@ -989,10 +989,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>0.9</v>
+        <v>159.9066666666667</v>
       </c>
       <c r="C51" t="n">
-        <v>10710.39415962658</v>
+        <v>94.47886581864022</v>
       </c>
     </row>
   </sheetData>
